--- a/estimation/notsensor/DenseModel/Dense_1st_torch_optimized/IWALQQ_1st_correction/angle/3_fold/190.xlsx
+++ b/estimation/notsensor/DenseModel/Dense_1st_torch_optimized/IWALQQ_1st_correction/angle/3_fold/190.xlsx
@@ -426,13 +426,13 @@
         <v>-7.629147769333431</v>
       </c>
       <c r="E2">
-        <v>-14.71070460588468</v>
+        <v>-17.92661400785381</v>
       </c>
       <c r="F2">
-        <v>3.889412418609959</v>
+        <v>2.815476098055823</v>
       </c>
       <c r="G2">
-        <v>-14.04797671310277</v>
+        <v>-15.85164799708173</v>
       </c>
     </row>
     <row r="3" spans="1:7">
@@ -449,13 +449,13 @@
         <v>-7.623269104785996</v>
       </c>
       <c r="E3">
-        <v>-15.90619910153962</v>
+        <v>-17.13174907918346</v>
       </c>
       <c r="F3">
-        <v>4.03510227688898</v>
+        <v>2.963395814263783</v>
       </c>
       <c r="G3">
-        <v>-14.10025850353171</v>
+        <v>-15.19952846039224</v>
       </c>
     </row>
     <row r="4" spans="1:7">
@@ -472,13 +472,13 @@
         <v>-7.613094812193061</v>
       </c>
       <c r="E4">
-        <v>-16.8136147231966</v>
+        <v>-18.14979984932184</v>
       </c>
       <c r="F4">
-        <v>3.844083587898251</v>
+        <v>2.820162283859608</v>
       </c>
       <c r="G4">
-        <v>-13.78307348014137</v>
+        <v>-16.05567857393978</v>
       </c>
     </row>
     <row r="5" spans="1:7">
@@ -495,13 +495,13 @@
         <v>-7.582230388848052</v>
       </c>
       <c r="E5">
-        <v>-16.21120993985225</v>
+        <v>-17.68410516779505</v>
       </c>
       <c r="F5">
-        <v>4.164365937413064</v>
+        <v>3.214003022028836</v>
       </c>
       <c r="G5">
-        <v>-13.32593017826003</v>
+        <v>-15.11302721599663</v>
       </c>
     </row>
     <row r="6" spans="1:7">
@@ -518,13 +518,13 @@
         <v>-7.514292660976313</v>
       </c>
       <c r="E6">
-        <v>-17.19333632568778</v>
+        <v>-20.89656387257033</v>
       </c>
       <c r="F6">
-        <v>4.240133595819517</v>
+        <v>2.964575675170785</v>
       </c>
       <c r="G6">
-        <v>-12.64220982912543</v>
+        <v>-13.83796894627356</v>
       </c>
     </row>
     <row r="7" spans="1:7">
@@ -541,13 +541,13 @@
         <v>-7.38851028054607</v>
       </c>
       <c r="E7">
-        <v>-18.30062973309532</v>
+        <v>-20.29219373150664</v>
       </c>
       <c r="F7">
-        <v>4.613096338905508</v>
+        <v>3.68156210314994</v>
       </c>
       <c r="G7">
-        <v>-12.49530437082027</v>
+        <v>-13.84855110508984</v>
       </c>
     </row>
     <row r="8" spans="1:7">
@@ -564,13 +564,13 @@
         <v>-7.179326091716071</v>
       </c>
       <c r="E8">
-        <v>-19.02700602087366</v>
+        <v>-21.86727850390653</v>
       </c>
       <c r="F8">
-        <v>4.46242889293426</v>
+        <v>3.62637153570279</v>
       </c>
       <c r="G8">
-        <v>-11.23711167534702</v>
+        <v>-13.4782914156139</v>
       </c>
     </row>
     <row r="9" spans="1:7">
@@ -587,13 +587,13 @@
         <v>-6.871701669907707</v>
       </c>
       <c r="E9">
-        <v>-20.5330496785526</v>
+        <v>-22.79781198537268</v>
       </c>
       <c r="F9">
-        <v>4.401765037843352</v>
+        <v>3.510320733631219</v>
       </c>
       <c r="G9">
-        <v>-10.83944563462422</v>
+        <v>-11.8486025419058</v>
       </c>
     </row>
     <row r="10" spans="1:7">
@@ -610,13 +610,13 @@
         <v>-6.450754225679202</v>
       </c>
       <c r="E10">
-        <v>-19.79944594625802</v>
+        <v>-20.69323991809994</v>
       </c>
       <c r="F10">
-        <v>4.619678220690074</v>
+        <v>3.626286015583357</v>
       </c>
       <c r="G10">
-        <v>-9.916131173175948</v>
+        <v>-11.90818242997606</v>
       </c>
     </row>
     <row r="11" spans="1:7">
@@ -633,13 +633,13 @@
         <v>-5.920642881009999</v>
       </c>
       <c r="E11">
-        <v>-20.29496062912533</v>
+        <v>-24.12496733432662</v>
       </c>
       <c r="F11">
-        <v>4.757311766977255</v>
+        <v>4.014745321051922</v>
       </c>
       <c r="G11">
-        <v>-9.078894206294265</v>
+        <v>-11.80490665133296</v>
       </c>
     </row>
     <row r="12" spans="1:7">
@@ -656,13 +656,13 @@
         <v>-5.301088211624118</v>
       </c>
       <c r="E12">
-        <v>-22.05816274027785</v>
+        <v>-22.61614319360696</v>
       </c>
       <c r="F12">
-        <v>5.173224614489962</v>
+        <v>4.174528578272438</v>
       </c>
       <c r="G12">
-        <v>-9.54782967138649</v>
+        <v>-11.17355913262963</v>
       </c>
     </row>
     <row r="13" spans="1:7">
@@ -679,13 +679,13 @@
         <v>-4.621527887333629</v>
       </c>
       <c r="E13">
-        <v>-22.53379742225149</v>
+        <v>-24.05152907134423</v>
       </c>
       <c r="F13">
-        <v>4.820042358287811</v>
+        <v>3.961904973183284</v>
       </c>
       <c r="G13">
-        <v>-7.669439374586176</v>
+        <v>-9.612630289772184</v>
       </c>
     </row>
     <row r="14" spans="1:7">
@@ -702,13 +702,13 @@
         <v>-3.932870634165545</v>
       </c>
       <c r="E14">
-        <v>-23.09287376629045</v>
+        <v>-25.66183631457578</v>
       </c>
       <c r="F14">
-        <v>4.885896017663613</v>
+        <v>3.898076873673328</v>
       </c>
       <c r="G14">
-        <v>-7.363922368948995</v>
+        <v>-10.37189397756741</v>
       </c>
     </row>
     <row r="15" spans="1:7">
@@ -725,13 +725,13 @@
         <v>-3.276897643565058</v>
       </c>
       <c r="E15">
-        <v>-23.81681826352667</v>
+        <v>-24.98399168273764</v>
       </c>
       <c r="F15">
-        <v>5.129298947219334</v>
+        <v>4.348758400853594</v>
       </c>
       <c r="G15">
-        <v>-6.644186594892663</v>
+        <v>-9.25293951693037</v>
       </c>
     </row>
     <row r="16" spans="1:7">
@@ -748,13 +748,13 @@
         <v>-2.689717645892516</v>
       </c>
       <c r="E16">
-        <v>-24.2061357024401</v>
+        <v>-26.24341917443287</v>
       </c>
       <c r="F16">
-        <v>5.260691108493767</v>
+        <v>4.455533437378437</v>
       </c>
       <c r="G16">
-        <v>-5.900350049310439</v>
+        <v>-7.270627885106793</v>
       </c>
     </row>
     <row r="17" spans="1:7">
@@ -771,13 +771,13 @@
         <v>-2.196367654781571</v>
       </c>
       <c r="E17">
-        <v>-26.51463853970026</v>
+        <v>-26.8713736081285</v>
       </c>
       <c r="F17">
-        <v>5.501449249170703</v>
+        <v>4.942646535437471</v>
       </c>
       <c r="G17">
-        <v>-6.435430214277301</v>
+        <v>-7.278291798030207</v>
       </c>
     </row>
     <row r="18" spans="1:7">
@@ -794,13 +794,13 @@
         <v>-1.801718782724916</v>
       </c>
       <c r="E18">
-        <v>-26.85376690118668</v>
+        <v>-28.53785204295119</v>
       </c>
       <c r="F18">
-        <v>5.498281837339824</v>
+        <v>4.920534833446106</v>
       </c>
       <c r="G18">
-        <v>-5.115512397224339</v>
+        <v>-7.191634957994244</v>
       </c>
     </row>
     <row r="19" spans="1:7">
@@ -817,13 +817,13 @@
         <v>-1.508841486063397</v>
       </c>
       <c r="E19">
-        <v>-28.61205561804088</v>
+        <v>-29.72944299401151</v>
       </c>
       <c r="F19">
-        <v>6.070476368294011</v>
+        <v>4.794484512224449</v>
       </c>
       <c r="G19">
-        <v>-4.999345354251314</v>
+        <v>-6.658703337082368</v>
       </c>
     </row>
     <row r="20" spans="1:7">
@@ -840,13 +840,13 @@
         <v>-1.31039499262026</v>
       </c>
       <c r="E20">
-        <v>-28.99221195403679</v>
+        <v>-30.19622677353716</v>
       </c>
       <c r="F20">
-        <v>5.911553063385579</v>
+        <v>4.921519898525509</v>
       </c>
       <c r="G20">
-        <v>-5.04205801279899</v>
+        <v>-7.202897433918844</v>
       </c>
     </row>
     <row r="21" spans="1:7">
@@ -863,13 +863,13 @@
         <v>-1.194857886652818</v>
       </c>
       <c r="E21">
-        <v>-29.61679720307071</v>
+        <v>-30.92468389512202</v>
       </c>
       <c r="F21">
-        <v>5.819571423816855</v>
+        <v>4.634213473581977</v>
       </c>
       <c r="G21">
-        <v>-4.157837783623971</v>
+        <v>-6.250294576084639</v>
       </c>
     </row>
     <row r="22" spans="1:7">
@@ -886,13 +886,13 @@
         <v>-1.154822125309438</v>
       </c>
       <c r="E22">
-        <v>-29.25788846711879</v>
+        <v>-32.85176921637513</v>
       </c>
       <c r="F22">
-        <v>5.956747279094474</v>
+        <v>5.204718190324391</v>
       </c>
       <c r="G22">
-        <v>-4.054429583159296</v>
+        <v>-6.356755099536522</v>
       </c>
     </row>
     <row r="23" spans="1:7">
@@ -909,13 +909,13 @@
         <v>-1.179040041167218</v>
       </c>
       <c r="E23">
-        <v>-29.04828804767377</v>
+        <v>-31.36756638883518</v>
       </c>
       <c r="F23">
-        <v>5.675995812934946</v>
+        <v>4.726706650161387</v>
       </c>
       <c r="G23">
-        <v>-4.213653581416083</v>
+        <v>-5.972132608238455</v>
       </c>
     </row>
     <row r="24" spans="1:7">
@@ -932,13 +932,13 @@
         <v>-1.259027419630286</v>
       </c>
       <c r="E24">
-        <v>-28.92156775951713</v>
+        <v>-32.52086909216065</v>
       </c>
       <c r="F24">
-        <v>5.638894334453946</v>
+        <v>5.256833200883757</v>
       </c>
       <c r="G24">
-        <v>-3.631851687253486</v>
+        <v>-5.358963295091264</v>
       </c>
     </row>
     <row r="25" spans="1:7">
@@ -955,13 +955,13 @@
         <v>-1.390601870022744</v>
       </c>
       <c r="E25">
-        <v>-29.7312634405626</v>
+        <v>-30.96071696280105</v>
       </c>
       <c r="F25">
-        <v>5.763595338235648</v>
+        <v>4.826000259941694</v>
       </c>
       <c r="G25">
-        <v>-3.828034615910696</v>
+        <v>-4.9756054321892</v>
       </c>
     </row>
     <row r="26" spans="1:7">
@@ -978,13 +978,13 @@
         <v>-1.567639970589298</v>
       </c>
       <c r="E26">
-        <v>-30.06869815277015</v>
+        <v>-33.87133476106908</v>
       </c>
       <c r="F26">
-        <v>6.057330025489949</v>
+        <v>4.44640970759959</v>
       </c>
       <c r="G26">
-        <v>-2.88034129711123</v>
+        <v>-6.269161375112946</v>
       </c>
     </row>
     <row r="27" spans="1:7">
@@ -1001,13 +1001,13 @@
         <v>-1.786622496959565</v>
       </c>
       <c r="E27">
-        <v>-30.44613061165044</v>
+        <v>-31.35160351795814</v>
       </c>
       <c r="F27">
-        <v>5.581776396907707</v>
+        <v>4.787069601128361</v>
       </c>
       <c r="G27">
-        <v>-4.167610514055899</v>
+        <v>-4.683602073443324</v>
       </c>
     </row>
     <row r="28" spans="1:7">
@@ -1024,13 +1024,13 @@
         <v>-2.04523253985177</v>
       </c>
       <c r="E28">
-        <v>-30.10833135728528</v>
+        <v>-33.11428032612577</v>
       </c>
       <c r="F28">
-        <v>5.588038370097355</v>
+        <v>4.623263730882629</v>
       </c>
       <c r="G28">
-        <v>-2.580260207249533</v>
+        <v>-4.289021461163131</v>
       </c>
     </row>
     <row r="29" spans="1:7">
@@ -1047,13 +1047,13 @@
         <v>-2.336065741440858</v>
       </c>
       <c r="E29">
-        <v>-30.47484340109608</v>
+        <v>-30.67996063127351</v>
       </c>
       <c r="F29">
-        <v>5.682265704654171</v>
+        <v>4.512234860268915</v>
       </c>
       <c r="G29">
-        <v>-2.906395290505294</v>
+        <v>-5.197978086607585</v>
       </c>
     </row>
     <row r="30" spans="1:7">
@@ -1070,13 +1070,13 @@
         <v>-2.653635160418862</v>
       </c>
       <c r="E30">
-        <v>-29.3516459929736</v>
+        <v>-30.80208678254936</v>
       </c>
       <c r="F30">
-        <v>5.548558165331364</v>
+        <v>4.865482048413599</v>
       </c>
       <c r="G30">
-        <v>-3.567173559052745</v>
+        <v>-3.987510215628468</v>
       </c>
     </row>
     <row r="31" spans="1:7">
@@ -1093,13 +1093,13 @@
         <v>-2.991048523266025</v>
       </c>
       <c r="E31">
-        <v>-29.95631274908479</v>
+        <v>-32.44754630526545</v>
       </c>
       <c r="F31">
-        <v>5.205715925051118</v>
+        <v>4.522403835951952</v>
       </c>
       <c r="G31">
-        <v>-3.905524555348417</v>
+        <v>-5.249079667551775</v>
       </c>
     </row>
     <row r="32" spans="1:7">
@@ -1116,13 +1116,13 @@
         <v>-3.336686110155545</v>
       </c>
       <c r="E32">
-        <v>-29.15018776979437</v>
+        <v>-32.40558546511038</v>
       </c>
       <c r="F32">
-        <v>5.682601450308244</v>
+        <v>4.246953033491399</v>
       </c>
       <c r="G32">
-        <v>-3.153775805927334</v>
+        <v>-4.527582683268552</v>
       </c>
     </row>
     <row r="33" spans="1:7">
@@ -1139,13 +1139,13 @@
         <v>-3.687228642382319</v>
       </c>
       <c r="E33">
-        <v>-29.13345505833603</v>
+        <v>-31.08306500930329</v>
       </c>
       <c r="F33">
-        <v>5.236973528704146</v>
+        <v>4.68347147866989</v>
       </c>
       <c r="G33">
-        <v>-3.917598114930139</v>
+        <v>-5.055760360786034</v>
       </c>
     </row>
     <row r="34" spans="1:7">
@@ -1162,13 +1162,13 @@
         <v>-4.035066927507101</v>
       </c>
       <c r="E34">
-        <v>-27.66289652298119</v>
+        <v>-31.07685194296477</v>
       </c>
       <c r="F34">
-        <v>5.617677426304804</v>
+        <v>3.757039943373869</v>
       </c>
       <c r="G34">
-        <v>-3.95202447799302</v>
+        <v>-4.869797086208553</v>
       </c>
     </row>
     <row r="35" spans="1:7">
@@ -1185,13 +1185,13 @@
         <v>-4.375950412422772</v>
       </c>
       <c r="E35">
-        <v>-27.70173724454497</v>
+        <v>-30.52849223266495</v>
       </c>
       <c r="F35">
-        <v>5.509914157288727</v>
+        <v>4.722075894064642</v>
       </c>
       <c r="G35">
-        <v>-3.857299838477854</v>
+        <v>-6.093007246968325</v>
       </c>
     </row>
     <row r="36" spans="1:7">
@@ -1208,13 +1208,13 @@
         <v>-4.710019050570216</v>
       </c>
       <c r="E36">
-        <v>-26.54109841332708</v>
+        <v>-29.6129480001642</v>
       </c>
       <c r="F36">
-        <v>5.476694342006469</v>
+        <v>4.455726649500121</v>
       </c>
       <c r="G36">
-        <v>-3.975506177503071</v>
+        <v>-4.644289345164479</v>
       </c>
     </row>
     <row r="37" spans="1:7">
@@ -1231,13 +1231,13 @@
         <v>-5.029521477526817</v>
       </c>
       <c r="E37">
-        <v>-26.80254080321191</v>
+        <v>-28.84545316839621</v>
       </c>
       <c r="F37">
-        <v>5.30133375340169</v>
+        <v>4.938316683464659</v>
       </c>
       <c r="G37">
-        <v>-3.407608574605413</v>
+        <v>-7.166070925339992</v>
       </c>
     </row>
     <row r="38" spans="1:7">
@@ -1254,13 +1254,13 @@
         <v>-5.33607477666021</v>
       </c>
       <c r="E38">
-        <v>-26.71251021146541</v>
+        <v>-28.49834110723427</v>
       </c>
       <c r="F38">
-        <v>6.004054158494566</v>
+        <v>4.825469718460022</v>
       </c>
       <c r="G38">
-        <v>-4.000590181054129</v>
+        <v>-5.457968469988709</v>
       </c>
     </row>
     <row r="39" spans="1:7">
@@ -1277,13 +1277,13 @@
         <v>-5.625369918129378</v>
       </c>
       <c r="E39">
-        <v>-26.24080171645643</v>
+        <v>-29.52349705309068</v>
       </c>
       <c r="F39">
-        <v>5.797269677115637</v>
+        <v>4.774867147049901</v>
       </c>
       <c r="G39">
-        <v>-3.946734226221265</v>
+        <v>-5.61621916785695</v>
       </c>
     </row>
     <row r="40" spans="1:7">
@@ -1300,13 +1300,13 @@
         <v>-5.893175161978926</v>
       </c>
       <c r="E40">
-        <v>-25.08678351423775</v>
+        <v>-27.68430714808945</v>
       </c>
       <c r="F40">
-        <v>5.717309949151015</v>
+        <v>5.170432540961042</v>
       </c>
       <c r="G40">
-        <v>-4.023687857281624</v>
+        <v>-5.553593577890557</v>
       </c>
     </row>
     <row r="41" spans="1:7">
@@ -1323,13 +1323,13 @@
         <v>-6.140424277115249</v>
       </c>
       <c r="E41">
-        <v>-25.64200159842218</v>
+        <v>-28.25435145617499</v>
       </c>
       <c r="F41">
-        <v>5.813578680632832</v>
+        <v>4.483178607838347</v>
       </c>
       <c r="G41">
-        <v>-4.328423574171537</v>
+        <v>-6.132939047263014</v>
       </c>
     </row>
     <row r="42" spans="1:7">
@@ -1346,13 +1346,13 @@
         <v>-6.362199358495907</v>
       </c>
       <c r="E42">
-        <v>-24.34637801398365</v>
+        <v>-26.14920880117729</v>
       </c>
       <c r="F42">
-        <v>5.602515025870387</v>
+        <v>4.971848488812259</v>
       </c>
       <c r="G42">
-        <v>-4.577085270717274</v>
+        <v>-6.634655534285102</v>
       </c>
     </row>
     <row r="43" spans="1:7">
@@ -1369,13 +1369,13 @@
         <v>-6.561161015791436</v>
       </c>
       <c r="E43">
-        <v>-23.90115203497152</v>
+        <v>-26.78904142219504</v>
       </c>
       <c r="F43">
-        <v>5.960613105234062</v>
+        <v>4.978164308003032</v>
       </c>
       <c r="G43">
-        <v>-5.516591610398122</v>
+        <v>-6.15421592344391</v>
       </c>
     </row>
     <row r="44" spans="1:7">
@@ -1392,13 +1392,13 @@
         <v>-6.737759091550429</v>
       </c>
       <c r="E44">
-        <v>-24.18029170127833</v>
+        <v>-26.43651330611993</v>
       </c>
       <c r="F44">
-        <v>5.931132419618157</v>
+        <v>5.010988196806429</v>
       </c>
       <c r="G44">
-        <v>-4.982984638196235</v>
+        <v>-6.793892774724046</v>
       </c>
     </row>
     <row r="45" spans="1:7">
@@ -1415,13 +1415,13 @@
         <v>-6.891894593980375</v>
       </c>
       <c r="E45">
-        <v>-21.71345982728799</v>
+        <v>-25.0453706194376</v>
       </c>
       <c r="F45">
-        <v>5.681785841761792</v>
+        <v>4.984000264301426</v>
       </c>
       <c r="G45">
-        <v>-4.930442969942463</v>
+        <v>-6.962584933223149</v>
       </c>
     </row>
     <row r="46" spans="1:7">
@@ -1438,13 +1438,13 @@
         <v>-7.029623333710438</v>
       </c>
       <c r="E46">
-        <v>-23.01640142572292</v>
+        <v>-25.4256945089718</v>
       </c>
       <c r="F46">
-        <v>5.842676109417202</v>
+        <v>5.074840051905118</v>
       </c>
       <c r="G46">
-        <v>-5.188036518353154</v>
+        <v>-6.269945974405752</v>
       </c>
     </row>
     <row r="47" spans="1:7">
@@ -1461,13 +1461,13 @@
         <v>-7.150421945362189</v>
       </c>
       <c r="E47">
-        <v>-22.28596762523371</v>
+        <v>-24.85670533533004</v>
       </c>
       <c r="F47">
-        <v>5.864347541164075</v>
+        <v>5.4977972233297</v>
       </c>
       <c r="G47">
-        <v>-5.851440049513246</v>
+        <v>-7.591843497691198</v>
       </c>
     </row>
     <row r="48" spans="1:7">
@@ -1484,13 +1484,13 @@
         <v>-7.258142119585778</v>
       </c>
       <c r="E48">
-        <v>-21.82470631976042</v>
+        <v>-24.52505348443029</v>
       </c>
       <c r="F48">
-        <v>6.245040352823325</v>
+        <v>5.333783887609044</v>
       </c>
       <c r="G48">
-        <v>-6.564584527400888</v>
+        <v>-8.002377628925139</v>
       </c>
     </row>
     <row r="49" spans="1:7">
@@ -1507,13 +1507,13 @@
         <v>-7.355202475745632</v>
       </c>
       <c r="E49">
-        <v>-21.06260942900958</v>
+        <v>-23.19805663206661</v>
       </c>
       <c r="F49">
-        <v>6.08962178910576</v>
+        <v>5.770533553851188</v>
       </c>
       <c r="G49">
-        <v>-5.806032606896602</v>
+        <v>-7.388864019041864</v>
       </c>
     </row>
     <row r="50" spans="1:7">
@@ -1530,13 +1530,13 @@
         <v>-7.439520409000095</v>
       </c>
       <c r="E50">
-        <v>-21.21857913078176</v>
+        <v>-22.26364224837589</v>
       </c>
       <c r="F50">
-        <v>6.169763643250657</v>
+        <v>5.099846768309906</v>
       </c>
       <c r="G50">
-        <v>-6.09580134740347</v>
+        <v>-8.354401178298001</v>
       </c>
     </row>
     <row r="51" spans="1:7">
@@ -1553,13 +1553,13 @@
         <v>-7.516928086021897</v>
       </c>
       <c r="E51">
-        <v>-19.89192191396866</v>
+        <v>-23.03495911220636</v>
       </c>
       <c r="F51">
-        <v>6.070834285830901</v>
+        <v>4.966486060582581</v>
       </c>
       <c r="G51">
-        <v>-6.50171064651905</v>
+        <v>-8.897936476572163</v>
       </c>
     </row>
     <row r="52" spans="1:7">
@@ -1576,13 +1576,13 @@
         <v>-7.584689479527349</v>
       </c>
       <c r="E52">
-        <v>-18.00248406137832</v>
+        <v>-21.21775494851236</v>
       </c>
       <c r="F52">
-        <v>6.197158588175928</v>
+        <v>5.5993365280981</v>
       </c>
       <c r="G52">
-        <v>-6.360386767993102</v>
+        <v>-8.042266392127818</v>
       </c>
     </row>
     <row r="53" spans="1:7">
@@ -1599,13 +1599,13 @@
         <v>-7.644424777673073</v>
       </c>
       <c r="E53">
-        <v>-19.32651476326697</v>
+        <v>-21.75194279940517</v>
       </c>
       <c r="F53">
-        <v>6.109809288409866</v>
+        <v>5.694680375325301</v>
       </c>
       <c r="G53">
-        <v>-6.861477561908267</v>
+        <v>-7.380733319197414</v>
       </c>
     </row>
     <row r="54" spans="1:7">
@@ -1622,13 +1622,13 @@
         <v>-7.697444465005112</v>
       </c>
       <c r="E54">
-        <v>-19.08229868850731</v>
+        <v>-20.46380478250132</v>
       </c>
       <c r="F54">
-        <v>6.27343778359307</v>
+        <v>4.982139409850785</v>
       </c>
       <c r="G54">
-        <v>-5.55952607549693</v>
+        <v>-8.784507254760115</v>
       </c>
     </row>
     <row r="55" spans="1:7">
@@ -1645,13 +1645,13 @@
         <v>-7.741334329020481</v>
       </c>
       <c r="E55">
-        <v>-17.95987112096614</v>
+        <v>-20.10740482114965</v>
       </c>
       <c r="F55">
-        <v>5.880965367334781</v>
+        <v>4.804010503305817</v>
       </c>
       <c r="G55">
-        <v>-6.929472856739358</v>
+        <v>-7.723911090889343</v>
       </c>
     </row>
     <row r="56" spans="1:7">
@@ -1668,13 +1668,13 @@
         <v>-7.781117262796898</v>
       </c>
       <c r="E56">
-        <v>-16.40970654103046</v>
+        <v>-18.62589190717025</v>
       </c>
       <c r="F56">
-        <v>6.127798603903343</v>
+        <v>5.367798723260853</v>
       </c>
       <c r="G56">
-        <v>-7.230232608436607</v>
+        <v>-9.233897258988481</v>
       </c>
     </row>
     <row r="57" spans="1:7">
@@ -1691,13 +1691,13 @@
         <v>-7.814867423289503</v>
       </c>
       <c r="E57">
-        <v>-16.23619805942657</v>
+        <v>-17.34109137561005</v>
       </c>
       <c r="F57">
-        <v>6.132297912409106</v>
+        <v>5.290887629183451</v>
       </c>
       <c r="G57">
-        <v>-6.874670085882263</v>
+        <v>-8.157566072169555</v>
       </c>
     </row>
     <row r="58" spans="1:7">
@@ -1714,13 +1714,13 @@
         <v>-7.845891416499831</v>
       </c>
       <c r="E58">
-        <v>-16.02553797706376</v>
+        <v>-20.37479309740655</v>
       </c>
       <c r="F58">
-        <v>6.248378804893071</v>
+        <v>5.059408421465076</v>
       </c>
       <c r="G58">
-        <v>-6.702683934571586</v>
+        <v>-8.917816302535487</v>
       </c>
     </row>
     <row r="59" spans="1:7">
@@ -1737,13 +1737,13 @@
         <v>-7.879813934030309</v>
       </c>
       <c r="E59">
-        <v>-16.6021938572005</v>
+        <v>-17.83136208557647</v>
       </c>
       <c r="F59">
-        <v>6.085939672852363</v>
+        <v>5.987658051152021</v>
       </c>
       <c r="G59">
-        <v>-7.410733482874289</v>
+        <v>-9.959933001206046</v>
       </c>
     </row>
     <row r="60" spans="1:7">
@@ -1760,13 +1760,13 @@
         <v>-7.917637809004202</v>
       </c>
       <c r="E60">
-        <v>-15.96076268485804</v>
+        <v>-18.45590657834433</v>
       </c>
       <c r="F60">
-        <v>6.269823766694037</v>
+        <v>5.136832636259079</v>
       </c>
       <c r="G60">
-        <v>-7.9088017487121</v>
+        <v>-8.606188029832811</v>
       </c>
     </row>
     <row r="61" spans="1:7">
@@ -1783,13 +1783,13 @@
         <v>-7.96661897627323</v>
       </c>
       <c r="E61">
-        <v>-15.37938360633129</v>
+        <v>-18.42272192081612</v>
       </c>
       <c r="F61">
-        <v>6.024723104396966</v>
+        <v>5.259368714054375</v>
       </c>
       <c r="G61">
-        <v>-7.824101441089847</v>
+        <v>-9.763385912539515</v>
       </c>
     </row>
     <row r="62" spans="1:7">
@@ -1806,13 +1806,13 @@
         <v>-8.029888671908077</v>
       </c>
       <c r="E62">
-        <v>-15.19526943860144</v>
+        <v>-16.75213616006847</v>
       </c>
       <c r="F62">
-        <v>6.141025715709093</v>
+        <v>6.026390746725924</v>
       </c>
       <c r="G62">
-        <v>-7.644875126684783</v>
+        <v>-8.53256480758496</v>
       </c>
     </row>
     <row r="63" spans="1:7">
@@ -1829,13 +1829,13 @@
         <v>-8.108215986179324</v>
       </c>
       <c r="E63">
-        <v>-14.97759927847475</v>
+        <v>-16.41472861870497</v>
       </c>
       <c r="F63">
-        <v>5.84944486849979</v>
+        <v>5.972242257771134</v>
       </c>
       <c r="G63">
-        <v>-7.575906531465146</v>
+        <v>-8.666158562276708</v>
       </c>
     </row>
     <row r="64" spans="1:7">
@@ -1852,13 +1852,13 @@
         <v>-8.209343588929141</v>
       </c>
       <c r="E64">
-        <v>-14.54419261662264</v>
+        <v>-17.09055807960969</v>
       </c>
       <c r="F64">
-        <v>5.960160165342246</v>
+        <v>5.612041016951755</v>
       </c>
       <c r="G64">
-        <v>-8.041696978295063</v>
+        <v>-9.996223201407537</v>
       </c>
     </row>
     <row r="65" spans="1:7">
@@ -1875,13 +1875,13 @@
         <v>-8.330937208541002</v>
       </c>
       <c r="E65">
-        <v>-14.33140415147622</v>
+        <v>-17.49294922298326</v>
       </c>
       <c r="F65">
-        <v>6.026484185374935</v>
+        <v>5.197141741224929</v>
       </c>
       <c r="G65">
-        <v>-8.691351813830563</v>
+        <v>-8.758148691176437</v>
       </c>
     </row>
     <row r="66" spans="1:7">
@@ -1898,13 +1898,13 @@
         <v>-8.475343362484091</v>
       </c>
       <c r="E66">
-        <v>-14.31904141743528</v>
+        <v>-16.37268173754375</v>
       </c>
       <c r="F66">
-        <v>5.63913980887084</v>
+        <v>4.900976065390428</v>
       </c>
       <c r="G66">
-        <v>-7.931452501291794</v>
+        <v>-9.466857038041455</v>
       </c>
     </row>
     <row r="67" spans="1:7">
@@ -1921,13 +1921,13 @@
         <v>-8.642971114732584</v>
       </c>
       <c r="E67">
-        <v>-13.71495204176007</v>
+        <v>-16.78508986542229</v>
       </c>
       <c r="F67">
-        <v>5.956166059023507</v>
+        <v>4.869816651504157</v>
       </c>
       <c r="G67">
-        <v>-7.861259004222626</v>
+        <v>-10.34256585463501</v>
       </c>
     </row>
     <row r="68" spans="1:7">
@@ -1944,13 +1944,13 @@
         <v>-8.827492907749807</v>
       </c>
       <c r="E68">
-        <v>-13.21497681199521</v>
+        <v>-15.8867085494106</v>
       </c>
       <c r="F68">
-        <v>5.849988079628786</v>
+        <v>5.239504290757019</v>
       </c>
       <c r="G68">
-        <v>-7.670657655344628</v>
+        <v>-9.746588204473253</v>
       </c>
     </row>
     <row r="69" spans="1:7">
@@ -1967,13 +1967,13 @@
         <v>-9.031279047274499</v>
       </c>
       <c r="E69">
-        <v>-13.51410063409787</v>
+        <v>-16.04107064291006</v>
       </c>
       <c r="F69">
-        <v>5.645910151659343</v>
+        <v>4.787688830141298</v>
       </c>
       <c r="G69">
-        <v>-8.768745747447644</v>
+        <v>-10.93301820429172</v>
       </c>
     </row>
     <row r="70" spans="1:7">
@@ -1990,13 +1990,13 @@
         <v>-9.245873723408948</v>
       </c>
       <c r="E70">
-        <v>-13.15444922840869</v>
+        <v>-16.45871368674147</v>
       </c>
       <c r="F70">
-        <v>5.57948002333032</v>
+        <v>4.716846497131861</v>
       </c>
       <c r="G70">
-        <v>-8.699479203129473</v>
+        <v>-9.044434737775992</v>
       </c>
     </row>
     <row r="71" spans="1:7">
@@ -2013,13 +2013,13 @@
         <v>-9.467018783422244</v>
       </c>
       <c r="E71">
-        <v>-13.85558833054228</v>
+        <v>-17.39498021630132</v>
       </c>
       <c r="F71">
-        <v>5.457447564016134</v>
+        <v>5.358956893134954</v>
       </c>
       <c r="G71">
-        <v>-7.894771656716669</v>
+        <v>-9.927350612008539</v>
       </c>
     </row>
     <row r="72" spans="1:7">
@@ -2036,13 +2036,13 @@
         <v>-9.691072405679854</v>
       </c>
       <c r="E72">
-        <v>-13.54677357406321</v>
+        <v>-15.14012168213603</v>
       </c>
       <c r="F72">
-        <v>5.709047755390167</v>
+        <v>4.709444255683097</v>
       </c>
       <c r="G72">
-        <v>-8.806032421856456</v>
+        <v>-9.797179961404396</v>
       </c>
     </row>
     <row r="73" spans="1:7">
@@ -2059,13 +2059,13 @@
         <v>-9.907009049614489</v>
       </c>
       <c r="E73">
-        <v>-13.8361792909454</v>
+        <v>-16.58248140984511</v>
       </c>
       <c r="F73">
-        <v>5.455208203851702</v>
+        <v>4.873424333579528</v>
       </c>
       <c r="G73">
-        <v>-8.302018416230114</v>
+        <v>-11.01567921586178</v>
       </c>
     </row>
     <row r="74" spans="1:7">
@@ -2082,13 +2082,13 @@
         <v>-10.11048200238541</v>
       </c>
       <c r="E74">
-        <v>-13.32367830207533</v>
+        <v>-15.76781346433922</v>
       </c>
       <c r="F74">
-        <v>5.20327068311768</v>
+        <v>4.556444010898407</v>
       </c>
       <c r="G74">
-        <v>-8.242021399421903</v>
+        <v>-10.12628791455442</v>
       </c>
     </row>
     <row r="75" spans="1:7">
@@ -2105,13 +2105,13 @@
         <v>-10.29074061737887</v>
       </c>
       <c r="E75">
-        <v>-13.63266061209268</v>
+        <v>-16.44587546292972</v>
       </c>
       <c r="F75">
-        <v>5.336876865261897</v>
+        <v>4.883349418551587</v>
       </c>
       <c r="G75">
-        <v>-8.024538420765021</v>
+        <v>-9.635002956526579</v>
       </c>
     </row>
     <row r="76" spans="1:7">
@@ -2128,13 +2128,13 @@
         <v>-10.43773887019413</v>
       </c>
       <c r="E76">
-        <v>-12.77248150280971</v>
+        <v>-18.1801813814393</v>
       </c>
       <c r="F76">
-        <v>4.972033782404366</v>
+        <v>4.813843733334781</v>
       </c>
       <c r="G76">
-        <v>-7.997862044809573</v>
+        <v>-8.439511993567125</v>
       </c>
     </row>
     <row r="77" spans="1:7">
@@ -2151,13 +2151,13 @@
         <v>-10.5464772354552</v>
       </c>
       <c r="E77">
-        <v>-14.1171439322773</v>
+        <v>-16.44246552200195</v>
       </c>
       <c r="F77">
-        <v>5.322599756434211</v>
+        <v>4.117372631784229</v>
       </c>
       <c r="G77">
-        <v>-7.929558869243331</v>
+        <v>-9.566385279134105</v>
       </c>
     </row>
     <row r="78" spans="1:7">
@@ -2174,13 +2174,13 @@
         <v>-10.60486014187353</v>
       </c>
       <c r="E78">
-        <v>-14.44348841164007</v>
+        <v>-15.42823225545203</v>
       </c>
       <c r="F78">
-        <v>5.260873234674043</v>
+        <v>3.871076271521001</v>
       </c>
       <c r="G78">
-        <v>-7.9821170902248</v>
+        <v>-9.050797606302471</v>
       </c>
     </row>
     <row r="79" spans="1:7">
@@ -2197,13 +2197,13 @@
         <v>-10.60900329373294</v>
       </c>
       <c r="E79">
-        <v>-14.36668096399597</v>
+        <v>-17.90750384754144</v>
       </c>
       <c r="F79">
-        <v>4.866612814437223</v>
+        <v>4.494974049496541</v>
       </c>
       <c r="G79">
-        <v>-7.190393503417017</v>
+        <v>-9.235029465562913</v>
       </c>
     </row>
     <row r="80" spans="1:7">
@@ -2220,13 +2220,13 @@
         <v>-10.55236644358057</v>
       </c>
       <c r="E80">
-        <v>-16.20016046327353</v>
+        <v>-18.06681103465727</v>
       </c>
       <c r="F80">
-        <v>4.562579287614819</v>
+        <v>4.090842390288787</v>
       </c>
       <c r="G80">
-        <v>-7.127999651638373</v>
+        <v>-8.841736655497495</v>
       </c>
     </row>
     <row r="81" spans="1:7">
@@ -2243,13 +2243,13 @@
         <v>-10.43066155256071</v>
       </c>
       <c r="E81">
-        <v>-15.45034479403149</v>
+        <v>-17.73234700139876</v>
       </c>
       <c r="F81">
-        <v>4.833016077147091</v>
+        <v>4.565106882255861</v>
       </c>
       <c r="G81">
-        <v>-6.959267766592799</v>
+        <v>-8.47237577913547</v>
       </c>
     </row>
     <row r="82" spans="1:7">
@@ -2266,13 +2266,13 @@
         <v>-10.24806208809337</v>
       </c>
       <c r="E82">
-        <v>-15.30150743882139</v>
+        <v>-18.67272991383158</v>
       </c>
       <c r="F82">
-        <v>4.651984237659123</v>
+        <v>4.074892888014396</v>
       </c>
       <c r="G82">
-        <v>-5.938563676470246</v>
+        <v>-8.628424964220097</v>
       </c>
     </row>
     <row r="83" spans="1:7">
@@ -2289,13 +2289,13 @@
         <v>-10.00221824645458</v>
       </c>
       <c r="E83">
-        <v>-15.92752821411574</v>
+        <v>-18.06336486593744</v>
       </c>
       <c r="F83">
-        <v>4.698168269565168</v>
+        <v>4.367221244415787</v>
       </c>
       <c r="G83">
-        <v>-6.559658435638452</v>
+        <v>-9.349435298309047</v>
       </c>
     </row>
     <row r="84" spans="1:7">
@@ -2312,13 +2312,13 @@
         <v>-9.703598083677516</v>
       </c>
       <c r="E84">
-        <v>-17.54837321636314</v>
+        <v>-19.54923870038622</v>
       </c>
       <c r="F84">
-        <v>4.69810492132855</v>
+        <v>3.983365772043404</v>
       </c>
       <c r="G84">
-        <v>-5.880576160804372</v>
+        <v>-8.097830588458946</v>
       </c>
     </row>
     <row r="85" spans="1:7">
@@ -2335,13 +2335,13 @@
         <v>-9.359585895901393</v>
       </c>
       <c r="E85">
-        <v>-18.64708969400015</v>
+        <v>-20.64137983376409</v>
       </c>
       <c r="F85">
-        <v>4.783552190290171</v>
+        <v>3.813633674262097</v>
       </c>
       <c r="G85">
-        <v>-6.267469686342378</v>
+        <v>-8.000242327052309</v>
       </c>
     </row>
     <row r="86" spans="1:7">
@@ -2358,13 +2358,13 @@
         <v>-8.980571888015655</v>
       </c>
       <c r="E86">
-        <v>-20.00913240670919</v>
+        <v>-21.85606147378953</v>
       </c>
       <c r="F86">
-        <v>4.706389286972215</v>
+        <v>3.819422119383028</v>
       </c>
       <c r="G86">
-        <v>-5.514817157989073</v>
+        <v>-8.526460161610544</v>
       </c>
     </row>
     <row r="87" spans="1:7">
@@ -2381,13 +2381,13 @@
         <v>-8.584432218483107</v>
       </c>
       <c r="E87">
-        <v>-20.06138193980969</v>
+        <v>-21.3313109627287</v>
       </c>
       <c r="F87">
-        <v>4.409615468066185</v>
+        <v>3.815956970840047</v>
       </c>
       <c r="G87">
-        <v>-5.708821747681443</v>
+        <v>-6.728012918492549</v>
       </c>
     </row>
     <row r="88" spans="1:7">
@@ -2404,13 +2404,13 @@
         <v>-8.181722574102707</v>
       </c>
       <c r="E88">
-        <v>-21.40034754897564</v>
+        <v>-23.57275162840927</v>
       </c>
       <c r="F88">
-        <v>4.082990376360038</v>
+        <v>3.446008020111138</v>
       </c>
       <c r="G88">
-        <v>-4.705534437640996</v>
+        <v>-7.294682308995138</v>
       </c>
     </row>
     <row r="89" spans="1:7">
@@ -2427,13 +2427,13 @@
         <v>-7.792917351099148</v>
       </c>
       <c r="E89">
-        <v>-23.83865003671765</v>
+        <v>-26.65681903811909</v>
       </c>
       <c r="F89">
-        <v>4.489074744961528</v>
+        <v>3.637983267474793</v>
       </c>
       <c r="G89">
-        <v>-5.296764765499438</v>
+        <v>-6.150203542250313</v>
       </c>
     </row>
     <row r="90" spans="1:7">
@@ -2450,13 +2450,13 @@
         <v>-7.435585170072259</v>
       </c>
       <c r="E90">
-        <v>-24.80222326454376</v>
+        <v>-25.64364543448696</v>
       </c>
       <c r="F90">
-        <v>4.159812782906175</v>
+        <v>3.423861476589633</v>
       </c>
       <c r="G90">
-        <v>-5.044570716863298</v>
+        <v>-5.934521500366796</v>
       </c>
     </row>
     <row r="91" spans="1:7">
@@ -2473,13 +2473,13 @@
         <v>-7.122468060824305</v>
       </c>
       <c r="E91">
-        <v>-26.40114592412002</v>
+        <v>-28.77456896475414</v>
       </c>
       <c r="F91">
-        <v>3.963325557389433</v>
+        <v>3.347707393939812</v>
       </c>
       <c r="G91">
-        <v>-4.461100307748908</v>
+        <v>-6.606767498662282</v>
       </c>
     </row>
     <row r="92" spans="1:7">
@@ -2496,13 +2496,13 @@
         <v>-6.870741576754598</v>
       </c>
       <c r="E92">
-        <v>-27.38650111192302</v>
+        <v>-30.56664462617957</v>
       </c>
       <c r="F92">
-        <v>3.544413170872884</v>
+        <v>3.110579107221063</v>
       </c>
       <c r="G92">
-        <v>-4.355225750857476</v>
+        <v>-5.385798577232596</v>
       </c>
     </row>
     <row r="93" spans="1:7">
@@ -2519,13 +2519,13 @@
         <v>-6.687509714268496</v>
       </c>
       <c r="E93">
-        <v>-28.77566938393801</v>
+        <v>-30.61245466924116</v>
       </c>
       <c r="F93">
-        <v>3.592817558472375</v>
+        <v>2.956080676640368</v>
       </c>
       <c r="G93">
-        <v>-4.468178254111869</v>
+        <v>-5.054720849486703</v>
       </c>
     </row>
     <row r="94" spans="1:7">
@@ -2542,13 +2542,13 @@
         <v>-6.576970412453438</v>
       </c>
       <c r="E94">
-        <v>-32.07595557785505</v>
+        <v>-33.33930472804092</v>
       </c>
       <c r="F94">
-        <v>3.176811272310657</v>
+        <v>3.231485551629373</v>
       </c>
       <c r="G94">
-        <v>-3.674779531261215</v>
+        <v>-4.645583768470334</v>
       </c>
     </row>
     <row r="95" spans="1:7">
@@ -2565,13 +2565,13 @@
         <v>-6.543181196990981</v>
       </c>
       <c r="E95">
-        <v>-33.27188707125173</v>
+        <v>-34.50003412873897</v>
       </c>
       <c r="F95">
-        <v>2.959922747191224</v>
+        <v>2.988679679203774</v>
       </c>
       <c r="G95">
-        <v>-3.692371770256903</v>
+        <v>-5.73127717807432</v>
       </c>
     </row>
     <row r="96" spans="1:7">
@@ -2588,13 +2588,13 @@
         <v>-6.581670856444884</v>
       </c>
       <c r="E96">
-        <v>-35.58230318878012</v>
+        <v>-38.16848299524261</v>
       </c>
       <c r="F96">
-        <v>2.785015098478261</v>
+        <v>1.864544632247953</v>
       </c>
       <c r="G96">
-        <v>-3.212789590710382</v>
+        <v>-5.164601166480653</v>
       </c>
     </row>
     <row r="97" spans="1:7">
@@ -2611,13 +2611,13 @@
         <v>-6.686435792279754</v>
       </c>
       <c r="E97">
-        <v>-37.73465292107079</v>
+        <v>-38.93378378135388</v>
       </c>
       <c r="F97">
-        <v>2.332813213619173</v>
+        <v>1.605934958492184</v>
       </c>
       <c r="G97">
-        <v>-3.597352492188741</v>
+        <v>-4.846523951067478</v>
       </c>
     </row>
     <row r="98" spans="1:7">
@@ -2634,13 +2634,13 @@
         <v>-6.862003669365821</v>
       </c>
       <c r="E98">
-        <v>-39.49994492297785</v>
+        <v>-39.96545393707034</v>
       </c>
       <c r="F98">
-        <v>2.193770169067252</v>
+        <v>1.913946754574171</v>
       </c>
       <c r="G98">
-        <v>-3.166491611343675</v>
+        <v>-4.784947804037033</v>
       </c>
     </row>
     <row r="99" spans="1:7">
@@ -2657,13 +2657,13 @@
         <v>-7.087506362276828</v>
       </c>
       <c r="E99">
-        <v>-41.41054433460604</v>
+        <v>-43.60278992290428</v>
       </c>
       <c r="F99">
-        <v>1.816640695717741</v>
+        <v>2.17888016605029</v>
       </c>
       <c r="G99">
-        <v>-2.87552776389713</v>
+        <v>-4.596776395584859</v>
       </c>
     </row>
     <row r="100" spans="1:7">
@@ -2680,13 +2680,13 @@
         <v>-7.383948548046692</v>
       </c>
       <c r="E100">
-        <v>-43.7847009880294</v>
+        <v>-45.33434252921719</v>
       </c>
       <c r="F100">
-        <v>1.323773994067915</v>
+        <v>1.444740619301011</v>
       </c>
       <c r="G100">
-        <v>-3.317157849381446</v>
+        <v>-4.630034136072378</v>
       </c>
     </row>
     <row r="101" spans="1:7">
@@ -2703,13 +2703,13 @@
         <v>-7.706990517797084</v>
       </c>
       <c r="E101">
-        <v>-46.53980419616301</v>
+        <v>-47.63290989450451</v>
       </c>
       <c r="F101">
-        <v>1.549564530138032</v>
+        <v>1.139345105391329</v>
       </c>
       <c r="G101">
-        <v>-3.527162305665113</v>
+        <v>-5.45896163365049</v>
       </c>
     </row>
     <row r="102" spans="1:7">
@@ -2726,13 +2726,13 @@
         <v>-8.112432217941812</v>
       </c>
       <c r="E102">
-        <v>-47.70165892265197</v>
+        <v>-49.42323643284448</v>
       </c>
       <c r="F102">
-        <v>1.11925579585398</v>
+        <v>0.7476249494428746</v>
       </c>
       <c r="G102">
-        <v>-2.923365146939599</v>
+        <v>-5.748955491254028</v>
       </c>
     </row>
   </sheetData>
